--- a/doc/FPGA_MSXtR_TangFPGA_pin_DUAL_NANO20K.xlsx
+++ b/doc/FPGA_MSXtR_TangFPGA_pin_DUAL_NANO20K.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\HRA_product\FPGA_MSXtR\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hra\Documents\github\HRA_product\FPGA_MSXtR\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28F0E6AC-F736-4B7E-B601-5E39E2BE48CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9506F22-6198-4C4D-9176-8933AD71853C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TangNano20K(CPU)" sheetId="5" r:id="rId1"/>
@@ -19,17 +19,28 @@
     <sheet name="IO Expander" sheetId="6" r:id="rId4"/>
     <sheet name="IO Expander Timing_x0009__x0009__x0009__x0009__x0009__x0009__x0009__x0009__x0009__x0009__x0009__x0009__x0009_" sheetId="7" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="276">
   <si>
     <t>#</t>
     <phoneticPr fontId="1"/>
@@ -1088,7 +1099,19 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>srom2_clk</t>
+    <t>srom_clk</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>srom2_cs_n</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BIOS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ext ROM</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1796,7 +1819,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2184,24 +2207,24 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2228,6 +2251,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3076,14 +3105,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="B1" s="129" t="s">
+      <c r="B1" s="130" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="129"/>
-      <c r="G1" s="129"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
       <c r="H1" s="18"/>
     </row>
     <row r="2" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
@@ -3273,7 +3302,7 @@
       <c r="O7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P7" s="134" t="s">
+      <c r="P7" s="129" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3315,7 +3344,7 @@
       <c r="O8" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P8" s="134"/>
+      <c r="P8" s="129"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B9" s="8">
@@ -3355,7 +3384,7 @@
       <c r="O9" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P9" s="134"/>
+      <c r="P9" s="129"/>
     </row>
     <row r="10" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="8">
@@ -3580,7 +3609,9 @@
       <c r="G15" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H15" s="17"/>
+      <c r="H15" s="17" t="s">
+        <v>274</v>
+      </c>
       <c r="J15" s="8">
         <v>29</v>
       </c>
@@ -3599,7 +3630,7 @@
       <c r="O15" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P15" s="134" t="s">
+      <c r="P15" s="129" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3622,7 +3653,7 @@
       <c r="G16" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H16" s="134" t="s">
+      <c r="H16" s="129" t="s">
         <v>70</v>
       </c>
       <c r="J16" s="8">
@@ -3641,7 +3672,7 @@
       <c r="O16" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P16" s="134"/>
+      <c r="P16" s="129"/>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B17" s="8">
@@ -3662,7 +3693,7 @@
       <c r="G17" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H17" s="134"/>
+      <c r="H17" s="129"/>
       <c r="J17" s="8">
         <v>27</v>
       </c>
@@ -3701,7 +3732,7 @@
       <c r="G18" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H18" s="134"/>
+      <c r="H18" s="129"/>
       <c r="J18" s="5">
         <v>26</v>
       </c>
@@ -3740,7 +3771,7 @@
       <c r="G19" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H19" s="134"/>
+      <c r="H19" s="129"/>
       <c r="J19" s="5">
         <v>25</v>
       </c>
@@ -3779,7 +3810,7 @@
       <c r="G20" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="134"/>
+      <c r="H20" s="129"/>
       <c r="J20" s="8">
         <v>24</v>
       </c>
@@ -3796,7 +3827,7 @@
       <c r="O20" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="P20" s="134" t="s">
+      <c r="P20" s="129" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3819,7 +3850,7 @@
       <c r="G21" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H21" s="134"/>
+      <c r="H21" s="129"/>
       <c r="J21" s="8">
         <v>23</v>
       </c>
@@ -3836,7 +3867,7 @@
       <c r="O21" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="P21" s="134"/>
+      <c r="P21" s="129"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B22" s="5">
@@ -3869,11 +3900,14 @@
       <c r="M22" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="N22" s="25" t="s">
-        <v>81</v>
+      <c r="N22" s="144" t="s">
+        <v>273</v>
       </c>
       <c r="O22" s="9" t="s">
         <v>7</v>
+      </c>
+      <c r="P22" s="145" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="23" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3962,14 +3996,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="B1" s="129" t="s">
+      <c r="B1" s="130" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="129"/>
-      <c r="G1" s="129"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
     </row>
     <row r="2" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:16" x14ac:dyDescent="0.15">
@@ -4027,7 +4061,7 @@
       <c r="G4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="132"/>
+      <c r="H4" s="133"/>
       <c r="J4" s="5">
         <v>40</v>
       </c>
@@ -4064,7 +4098,7 @@
       <c r="G5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="132"/>
+      <c r="H5" s="133"/>
       <c r="J5" s="5">
         <v>39</v>
       </c>
@@ -4101,7 +4135,7 @@
       <c r="G6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="132"/>
+      <c r="H6" s="133"/>
       <c r="J6" s="8">
         <v>38</v>
       </c>
@@ -4139,7 +4173,7 @@
       <c r="G7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="132"/>
+      <c r="H7" s="133"/>
       <c r="J7" s="8">
         <v>37</v>
       </c>
@@ -4213,7 +4247,7 @@
       <c r="G9" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="132"/>
+      <c r="H9" s="133"/>
       <c r="J9" s="8">
         <v>35</v>
       </c>
@@ -4249,7 +4283,7 @@
       <c r="G10" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H10" s="132"/>
+      <c r="H10" s="133"/>
       <c r="J10" s="8">
         <v>34</v>
       </c>
@@ -4287,7 +4321,7 @@
       </c>
       <c r="F11" s="33"/>
       <c r="G11" s="9"/>
-      <c r="H11" s="133"/>
+      <c r="H11" s="134"/>
       <c r="J11" s="8">
         <v>33</v>
       </c>
@@ -4323,7 +4357,7 @@
       </c>
       <c r="F12" s="33"/>
       <c r="G12" s="9"/>
-      <c r="H12" s="133"/>
+      <c r="H12" s="134"/>
       <c r="J12" s="8">
         <v>32</v>
       </c>
@@ -4359,7 +4393,7 @@
       </c>
       <c r="F13" s="33"/>
       <c r="G13" s="9"/>
-      <c r="H13" s="133"/>
+      <c r="H13" s="134"/>
       <c r="J13" s="8">
         <v>31</v>
       </c>
@@ -4391,7 +4425,7 @@
       </c>
       <c r="F14" s="33"/>
       <c r="G14" s="9"/>
-      <c r="H14" s="133"/>
+      <c r="H14" s="134"/>
       <c r="J14" s="8">
         <v>30</v>
       </c>
@@ -4429,7 +4463,7 @@
       </c>
       <c r="F15" s="33"/>
       <c r="G15" s="9"/>
-      <c r="H15" s="133"/>
+      <c r="H15" s="134"/>
       <c r="J15" s="8">
         <v>29</v>
       </c>
@@ -4461,7 +4495,7 @@
       </c>
       <c r="F16" s="33"/>
       <c r="G16" s="9"/>
-      <c r="H16" s="133"/>
+      <c r="H16" s="134"/>
       <c r="J16" s="8">
         <v>28</v>
       </c>
@@ -4497,7 +4531,7 @@
       </c>
       <c r="F17" s="33"/>
       <c r="G17" s="9"/>
-      <c r="H17" s="133"/>
+      <c r="H17" s="134"/>
       <c r="J17" s="8">
         <v>27</v>
       </c>
@@ -4536,7 +4570,7 @@
       <c r="G18" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H18" s="130" t="s">
+      <c r="H18" s="132" t="s">
         <v>56</v>
       </c>
       <c r="J18" s="5">
@@ -4577,7 +4611,7 @@
       <c r="G19" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H19" s="130"/>
+      <c r="H19" s="132"/>
       <c r="J19" s="5">
         <v>25</v>
       </c>
@@ -4616,7 +4650,7 @@
       <c r="G20" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H20" s="130"/>
+      <c r="H20" s="132"/>
       <c r="J20" s="8">
         <v>24</v>
       </c>
@@ -4654,7 +4688,7 @@
       <c r="G21" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H21" s="130"/>
+      <c r="H21" s="132"/>
       <c r="J21" s="8">
         <v>23</v>
       </c>
@@ -4785,13 +4819,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="B1" s="129" t="s">
+      <c r="B1" s="130" t="s">
         <v>256</v>
       </c>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="129"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
       <c r="G1" s="18"/>
     </row>
     <row r="2" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
@@ -6272,7 +6306,7 @@
       <c r="E11" s="96"/>
     </row>
     <row r="12" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="129" t="s">
+      <c r="A12" s="130" t="s">
         <v>197</v>
       </c>
       <c r="B12" s="78"/>
@@ -6333,7 +6367,7 @@
       <c r="BA12" s="101"/>
     </row>
     <row r="13" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="129"/>
+      <c r="A13" s="130"/>
       <c r="B13" s="78"/>
       <c r="C13" s="75"/>
       <c r="D13" s="75"/>
@@ -6395,7 +6429,7 @@
       <c r="BD13" s="87"/>
     </row>
     <row r="14" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="129"/>
+      <c r="A14" s="130"/>
       <c r="B14" s="78"/>
       <c r="C14" s="75"/>
       <c r="D14" s="75"/>
@@ -6460,7 +6494,7 @@
       <c r="BG14" s="81"/>
     </row>
     <row r="15" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="129"/>
+      <c r="A15" s="130"/>
       <c r="B15" s="78"/>
       <c r="C15" s="80"/>
       <c r="D15" s="80"/>

--- a/doc/FPGA_MSXtR_TangFPGA_pin_DUAL_NANO20K.xlsx
+++ b/doc/FPGA_MSXtR_TangFPGA_pin_DUAL_NANO20K.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hra\Documents\github\HRA_product\FPGA_MSXtR\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9506F22-6198-4C4D-9176-8933AD71853C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E19C5C-C456-4978-AAEC-0471AC52053D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1119,7 +1119,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1159,6 +1159,12 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Source Sans Pro SemiBold"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="22">
@@ -1819,7 +1825,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2207,24 +2213,30 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2252,11 +2264,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3105,14 +3114,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="B1" s="130" t="s">
+      <c r="B1" s="131" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
-      <c r="E1" s="130"/>
-      <c r="F1" s="130"/>
-      <c r="G1" s="130"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
       <c r="H1" s="18"/>
     </row>
     <row r="2" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
@@ -3302,7 +3311,7 @@
       <c r="O7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P7" s="129" t="s">
+      <c r="P7" s="136" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3344,7 +3353,7 @@
       <c r="O8" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P8" s="129"/>
+      <c r="P8" s="136"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B9" s="8">
@@ -3384,7 +3393,7 @@
       <c r="O9" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P9" s="129"/>
+      <c r="P9" s="136"/>
     </row>
     <row r="10" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="8">
@@ -3424,7 +3433,7 @@
       <c r="O10" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P10" s="131" t="s">
+      <c r="P10" s="133" t="s">
         <v>67</v>
       </c>
     </row>
@@ -3466,7 +3475,7 @@
       <c r="O11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P11" s="131"/>
+      <c r="P11" s="133"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B12" s="8">
@@ -3630,7 +3639,7 @@
       <c r="O15" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P15" s="129" t="s">
+      <c r="P15" s="136" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3653,7 +3662,7 @@
       <c r="G16" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H16" s="129" t="s">
+      <c r="H16" s="136" t="s">
         <v>70</v>
       </c>
       <c r="J16" s="8">
@@ -3672,7 +3681,7 @@
       <c r="O16" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P16" s="129"/>
+      <c r="P16" s="136"/>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B17" s="8">
@@ -3693,7 +3702,7 @@
       <c r="G17" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H17" s="129"/>
+      <c r="H17" s="136"/>
       <c r="J17" s="8">
         <v>27</v>
       </c>
@@ -3732,7 +3741,7 @@
       <c r="G18" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H18" s="129"/>
+      <c r="H18" s="136"/>
       <c r="J18" s="5">
         <v>26</v>
       </c>
@@ -3771,7 +3780,7 @@
       <c r="G19" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H19" s="129"/>
+      <c r="H19" s="136"/>
       <c r="J19" s="5">
         <v>25</v>
       </c>
@@ -3810,7 +3819,7 @@
       <c r="G20" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="129"/>
+      <c r="H20" s="136"/>
       <c r="J20" s="8">
         <v>24</v>
       </c>
@@ -3827,7 +3836,7 @@
       <c r="O20" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="P20" s="129" t="s">
+      <c r="P20" s="136" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3850,7 +3859,7 @@
       <c r="G21" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H21" s="129"/>
+      <c r="H21" s="136"/>
       <c r="J21" s="8">
         <v>23</v>
       </c>
@@ -3867,7 +3876,7 @@
       <c r="O21" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="P21" s="129"/>
+      <c r="P21" s="136"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B22" s="5">
@@ -3900,13 +3909,13 @@
       <c r="M22" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="N22" s="144" t="s">
+      <c r="N22" s="129" t="s">
         <v>273</v>
       </c>
       <c r="O22" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P22" s="145" t="s">
+      <c r="P22" s="130" t="s">
         <v>275</v>
       </c>
     </row>
@@ -3995,15 +4004,15 @@
     <col min="17" max="17" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="B1" s="130" t="s">
+    <row r="1" spans="2:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="B1" s="146" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
-      <c r="E1" s="130"/>
-      <c r="F1" s="130"/>
-      <c r="G1" s="130"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="146"/>
+      <c r="G1" s="146"/>
     </row>
     <row r="2" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:16" x14ac:dyDescent="0.15">
@@ -4061,7 +4070,7 @@
       <c r="G4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="133"/>
+      <c r="H4" s="134"/>
       <c r="J4" s="5">
         <v>40</v>
       </c>
@@ -4098,7 +4107,7 @@
       <c r="G5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="133"/>
+      <c r="H5" s="134"/>
       <c r="J5" s="5">
         <v>39</v>
       </c>
@@ -4135,7 +4144,7 @@
       <c r="G6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="133"/>
+      <c r="H6" s="134"/>
       <c r="J6" s="8">
         <v>38</v>
       </c>
@@ -4173,7 +4182,7 @@
       <c r="G7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="133"/>
+      <c r="H7" s="134"/>
       <c r="J7" s="8">
         <v>37</v>
       </c>
@@ -4247,7 +4256,7 @@
       <c r="G9" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="133"/>
+      <c r="H9" s="134"/>
       <c r="J9" s="8">
         <v>35</v>
       </c>
@@ -4283,7 +4292,7 @@
       <c r="G10" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H10" s="133"/>
+      <c r="H10" s="134"/>
       <c r="J10" s="8">
         <v>34</v>
       </c>
@@ -4302,7 +4311,7 @@
       <c r="O10" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="P10" s="131" t="s">
+      <c r="P10" s="133" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4321,7 +4330,7 @@
       </c>
       <c r="F11" s="33"/>
       <c r="G11" s="9"/>
-      <c r="H11" s="134"/>
+      <c r="H11" s="135"/>
       <c r="J11" s="8">
         <v>33</v>
       </c>
@@ -4340,7 +4349,7 @@
       <c r="O11" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="P11" s="131"/>
+      <c r="P11" s="133"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B12" s="8">
@@ -4357,7 +4366,7 @@
       </c>
       <c r="F12" s="33"/>
       <c r="G12" s="9"/>
-      <c r="H12" s="134"/>
+      <c r="H12" s="135"/>
       <c r="J12" s="8">
         <v>32</v>
       </c>
@@ -4393,7 +4402,7 @@
       </c>
       <c r="F13" s="33"/>
       <c r="G13" s="9"/>
-      <c r="H13" s="134"/>
+      <c r="H13" s="135"/>
       <c r="J13" s="8">
         <v>31</v>
       </c>
@@ -4425,7 +4434,7 @@
       </c>
       <c r="F14" s="33"/>
       <c r="G14" s="9"/>
-      <c r="H14" s="134"/>
+      <c r="H14" s="135"/>
       <c r="J14" s="8">
         <v>30</v>
       </c>
@@ -4463,7 +4472,7 @@
       </c>
       <c r="F15" s="33"/>
       <c r="G15" s="9"/>
-      <c r="H15" s="134"/>
+      <c r="H15" s="135"/>
       <c r="J15" s="8">
         <v>29</v>
       </c>
@@ -4495,7 +4504,7 @@
       </c>
       <c r="F16" s="33"/>
       <c r="G16" s="9"/>
-      <c r="H16" s="134"/>
+      <c r="H16" s="135"/>
       <c r="J16" s="8">
         <v>28</v>
       </c>
@@ -4531,7 +4540,7 @@
       </c>
       <c r="F17" s="33"/>
       <c r="G17" s="9"/>
-      <c r="H17" s="134"/>
+      <c r="H17" s="135"/>
       <c r="J17" s="8">
         <v>27</v>
       </c>
@@ -4792,7 +4801,8 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -4819,13 +4829,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="B1" s="130" t="s">
+      <c r="B1" s="131" t="s">
         <v>256</v>
       </c>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
-      <c r="E1" s="130"/>
-      <c r="F1" s="130"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
       <c r="G1" s="18"/>
     </row>
     <row r="2" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
@@ -5789,16 +5799,16 @@
       <c r="D15" s="67" t="s">
         <v>129</v>
       </c>
-      <c r="E15" s="138" t="s">
+      <c r="E15" s="140" t="s">
         <v>128</v>
       </c>
-      <c r="F15" s="139"/>
-      <c r="G15" s="139"/>
-      <c r="H15" s="139"/>
-      <c r="I15" s="139"/>
-      <c r="J15" s="139"/>
-      <c r="K15" s="139"/>
-      <c r="L15" s="140"/>
+      <c r="F15" s="141"/>
+      <c r="G15" s="141"/>
+      <c r="H15" s="141"/>
+      <c r="I15" s="141"/>
+      <c r="J15" s="141"/>
+      <c r="K15" s="141"/>
+      <c r="L15" s="142"/>
     </row>
     <row r="16" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="68">
@@ -5807,34 +5817,34 @@
       <c r="D16" s="69" t="s">
         <v>91</v>
       </c>
-      <c r="E16" s="135" t="s">
+      <c r="E16" s="137" t="s">
         <v>92</v>
       </c>
-      <c r="F16" s="136"/>
-      <c r="G16" s="136"/>
-      <c r="H16" s="136"/>
-      <c r="I16" s="136"/>
-      <c r="J16" s="136"/>
-      <c r="K16" s="136"/>
-      <c r="L16" s="137"/>
+      <c r="F16" s="138"/>
+      <c r="G16" s="138"/>
+      <c r="H16" s="138"/>
+      <c r="I16" s="138"/>
+      <c r="J16" s="138"/>
+      <c r="K16" s="138"/>
+      <c r="L16" s="139"/>
     </row>
     <row r="17" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="68"/>
       <c r="D17" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="E17" s="141" t="s">
+      <c r="E17" s="143" t="s">
         <v>159</v>
       </c>
-      <c r="F17" s="142"/>
-      <c r="G17" s="142"/>
-      <c r="H17" s="142"/>
-      <c r="I17" s="143"/>
-      <c r="J17" s="141" t="s">
+      <c r="F17" s="144"/>
+      <c r="G17" s="144"/>
+      <c r="H17" s="144"/>
+      <c r="I17" s="145"/>
+      <c r="J17" s="143" t="s">
         <v>109</v>
       </c>
-      <c r="K17" s="142"/>
-      <c r="L17" s="143"/>
+      <c r="K17" s="144"/>
+      <c r="L17" s="145"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -6306,7 +6316,7 @@
       <c r="E11" s="96"/>
     </row>
     <row r="12" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="130" t="s">
+      <c r="A12" s="131" t="s">
         <v>197</v>
       </c>
       <c r="B12" s="78"/>
@@ -6367,7 +6377,7 @@
       <c r="BA12" s="101"/>
     </row>
     <row r="13" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="130"/>
+      <c r="A13" s="131"/>
       <c r="B13" s="78"/>
       <c r="C13" s="75"/>
       <c r="D13" s="75"/>
@@ -6429,7 +6439,7 @@
       <c r="BD13" s="87"/>
     </row>
     <row r="14" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="130"/>
+      <c r="A14" s="131"/>
       <c r="B14" s="78"/>
       <c r="C14" s="75"/>
       <c r="D14" s="75"/>
@@ -6494,7 +6504,7 @@
       <c r="BG14" s="81"/>
     </row>
     <row r="15" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="130"/>
+      <c r="A15" s="131"/>
       <c r="B15" s="78"/>
       <c r="C15" s="80"/>
       <c r="D15" s="80"/>

--- a/doc/FPGA_MSXtR_TangFPGA_pin_DUAL_NANO20K.xlsx
+++ b/doc/FPGA_MSXtR_TangFPGA_pin_DUAL_NANO20K.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hra\Documents\github\HRA_product\FPGA_MSXtR\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E19C5C-C456-4978-AAEC-0471AC52053D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864B0B38-5F59-4A89-A5F2-E6E3FB20635B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TangNano20K(CPU)" sheetId="5" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="283">
   <si>
     <t>#</t>
     <phoneticPr fontId="1"/>
@@ -1112,6 +1112,34 @@
   </si>
   <si>
     <t>Ext ROM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SDA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SCL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I2C0_SCL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I2C0_SDA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Keyboard</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>groove</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ST-LINK</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1167,7 +1195,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1294,6 +1322,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="41">
     <border>
@@ -1825,7 +1871,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2219,24 +2265,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2264,8 +2313,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2480,6 +2541,50 @@
             </a14:hiddenFill>
           </a:ext>
         </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>11207</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>46884</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1400736</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>158626</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DD5C34F-33C7-1B1B-E118-88A94081D386}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6947648" y="6456649"/>
+          <a:ext cx="2812676" cy="784095"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -3114,14 +3219,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="B1" s="131" t="s">
+      <c r="B1" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
       <c r="H1" s="18"/>
     </row>
     <row r="2" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
@@ -4005,14 +4110,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="15" x14ac:dyDescent="0.15">
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="131" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
     </row>
     <row r="2" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:16" x14ac:dyDescent="0.15">
@@ -4808,7 +4913,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC74F05D-A8C1-40EC-9543-D575AFFCD60C}">
-  <dimension ref="B1:N26"/>
+  <dimension ref="B1:N38"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.25" customWidth="1"/>
@@ -4829,13 +4934,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="B1" s="131" t="s">
+      <c r="B1" s="137" t="s">
         <v>256</v>
       </c>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
       <c r="G1" s="18"/>
     </row>
     <row r="2" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
@@ -4890,7 +4995,9 @@
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="9"/>
+      <c r="M4" s="9" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B5" s="8">
@@ -4911,7 +5018,9 @@
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="9"/>
+      <c r="M5" s="9" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B6" s="5">
@@ -4979,7 +5088,9 @@
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
-      <c r="M8" s="9"/>
+      <c r="M8" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.15">
@@ -5217,9 +5328,15 @@
       <c r="J17" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="9"/>
+      <c r="K17" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="L17" s="147" t="s">
+        <v>278</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="18" spans="2:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="8">
@@ -5244,9 +5361,15 @@
       <c r="J18" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="9"/>
+      <c r="K18" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="L18" s="147" t="s">
+        <v>279</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B19" s="8">
@@ -5358,6 +5481,52 @@
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.15">
       <c r="C26" s="24"/>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="M30" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="L31" t="s">
+        <v>3</v>
+      </c>
+      <c r="M31" s="148"/>
+      <c r="N31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="L32" t="s">
+        <v>239</v>
+      </c>
+      <c r="M32" s="149"/>
+      <c r="N32" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="12:14" x14ac:dyDescent="0.15">
+      <c r="L33" t="s">
+        <v>247</v>
+      </c>
+      <c r="M33" s="150"/>
+      <c r="N33" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="34" spans="12:14" x14ac:dyDescent="0.15">
+      <c r="L34" t="s">
+        <v>246</v>
+      </c>
+      <c r="M34" s="151"/>
+      <c r="N34" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="38" spans="12:14" x14ac:dyDescent="0.15">
+      <c r="L38" t="s">
+        <v>282</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5799,16 +5968,16 @@
       <c r="D15" s="67" t="s">
         <v>129</v>
       </c>
-      <c r="E15" s="140" t="s">
+      <c r="E15" s="141" t="s">
         <v>128</v>
       </c>
-      <c r="F15" s="141"/>
-      <c r="G15" s="141"/>
-      <c r="H15" s="141"/>
-      <c r="I15" s="141"/>
-      <c r="J15" s="141"/>
-      <c r="K15" s="141"/>
-      <c r="L15" s="142"/>
+      <c r="F15" s="142"/>
+      <c r="G15" s="142"/>
+      <c r="H15" s="142"/>
+      <c r="I15" s="142"/>
+      <c r="J15" s="142"/>
+      <c r="K15" s="142"/>
+      <c r="L15" s="143"/>
     </row>
     <row r="16" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="68">
@@ -5817,34 +5986,34 @@
       <c r="D16" s="69" t="s">
         <v>91</v>
       </c>
-      <c r="E16" s="137" t="s">
+      <c r="E16" s="138" t="s">
         <v>92</v>
       </c>
-      <c r="F16" s="138"/>
-      <c r="G16" s="138"/>
-      <c r="H16" s="138"/>
-      <c r="I16" s="138"/>
-      <c r="J16" s="138"/>
-      <c r="K16" s="138"/>
-      <c r="L16" s="139"/>
+      <c r="F16" s="139"/>
+      <c r="G16" s="139"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="139"/>
+      <c r="J16" s="139"/>
+      <c r="K16" s="139"/>
+      <c r="L16" s="140"/>
     </row>
     <row r="17" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="68"/>
       <c r="D17" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="E17" s="143" t="s">
+      <c r="E17" s="144" t="s">
         <v>159</v>
       </c>
-      <c r="F17" s="144"/>
-      <c r="G17" s="144"/>
-      <c r="H17" s="144"/>
-      <c r="I17" s="145"/>
-      <c r="J17" s="143" t="s">
+      <c r="F17" s="145"/>
+      <c r="G17" s="145"/>
+      <c r="H17" s="145"/>
+      <c r="I17" s="146"/>
+      <c r="J17" s="144" t="s">
         <v>109</v>
       </c>
-      <c r="K17" s="144"/>
-      <c r="L17" s="145"/>
+      <c r="K17" s="145"/>
+      <c r="L17" s="146"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -6316,7 +6485,7 @@
       <c r="E11" s="96"/>
     </row>
     <row r="12" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="131" t="s">
+      <c r="A12" s="137" t="s">
         <v>197</v>
       </c>
       <c r="B12" s="78"/>
@@ -6377,7 +6546,7 @@
       <c r="BA12" s="101"/>
     </row>
     <row r="13" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="131"/>
+      <c r="A13" s="137"/>
       <c r="B13" s="78"/>
       <c r="C13" s="75"/>
       <c r="D13" s="75"/>
@@ -6439,7 +6608,7 @@
       <c r="BD13" s="87"/>
     </row>
     <row r="14" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="131"/>
+      <c r="A14" s="137"/>
       <c r="B14" s="78"/>
       <c r="C14" s="75"/>
       <c r="D14" s="75"/>
@@ -6504,7 +6673,7 @@
       <c r="BG14" s="81"/>
     </row>
     <row r="15" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="131"/>
+      <c r="A15" s="137"/>
       <c r="B15" s="78"/>
       <c r="C15" s="80"/>
       <c r="D15" s="80"/>
